--- a/research/traditional_assets/database/data/new_zealand/new_zealand_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_heathcare_information_and_technology.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.132</v>
+        <v>0.2355</v>
       </c>
       <c r="G2">
-        <v>-0.3987170618200114</v>
+        <v>-0.02589506867822557</v>
       </c>
       <c r="H2">
-        <v>-1.380416326017232</v>
+        <v>-0.9519252420625985</v>
       </c>
       <c r="I2">
-        <v>-1.436784322308648</v>
+        <v>-0.8787443266161608</v>
       </c>
       <c r="J2">
-        <v>-1.436784322308648</v>
+        <v>-0.8787443266161608</v>
       </c>
       <c r="K2">
-        <v>-23.1</v>
+        <v>-14.41</v>
       </c>
       <c r="L2">
-        <v>-1.45273882145777</v>
+        <v>-0.8111911731591984</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.89</v>
+        <v>9.82</v>
       </c>
       <c r="V2">
-        <v>0.0957170356111646</v>
+        <v>0.0948792270531401</v>
       </c>
       <c r="W2">
-        <v>-2.523789173789174</v>
+        <v>-0.4125615035371133</v>
       </c>
       <c r="X2">
-        <v>0.05649390623174897</v>
+        <v>0.1148641853510222</v>
       </c>
       <c r="Y2">
-        <v>-2.580283080020923</v>
+        <v>-0.5274256888881355</v>
       </c>
       <c r="Z2">
-        <v>0.3488856516195014</v>
-      </c>
-      <c r="AA2">
-        <v>5.860658249807416</v>
+        <v>0.7099920063948841</v>
       </c>
       <c r="AB2">
-        <v>0.0562789545266335</v>
-      </c>
-      <c r="AC2">
-        <v>5.804379295280784</v>
+        <v>0.1140100568502549</v>
       </c>
       <c r="AD2">
-        <v>1.91</v>
+        <v>1.499</v>
       </c>
       <c r="AE2">
-        <v>0.01653754514906939</v>
+        <v>0.03507109004739337</v>
       </c>
       <c r="AF2">
-        <v>1.926537545149069</v>
+        <v>1.534071090047393</v>
       </c>
       <c r="AG2">
-        <v>-17.96346245485093</v>
+        <v>-8.285928909952608</v>
       </c>
       <c r="AH2">
-        <v>0.009185950274577592</v>
+        <v>0.01460546158143494</v>
       </c>
       <c r="AI2">
-        <v>0.03348954460603591</v>
+        <v>0.04197865876156284</v>
       </c>
       <c r="AJ2">
-        <v>-0.09462594865637317</v>
+        <v>-0.08702420571972293</v>
       </c>
       <c r="AK2">
-        <v>-0.4772878597905513</v>
+        <v>-0.3100548895425766</v>
       </c>
       <c r="AL2">
-        <v>0.479</v>
+        <v>0.165</v>
       </c>
       <c r="AM2">
-        <v>0.241</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.08788478350894952</v>
+        <v>-0.1019519825885874</v>
       </c>
       <c r="AO2">
-        <v>-47.72442588726513</v>
+        <v>-94.78787878787878</v>
       </c>
       <c r="AP2">
-        <v>0.8265523606888571</v>
+        <v>0.5635536223867651</v>
       </c>
       <c r="AQ2">
-        <v>-94.85477178423237</v>
+        <v>-295.0943396226415</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adherium Limited (ASX:ADR)</t>
+          <t>Volpara Health Technologies Limited (ASX:VHT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.282</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="G3">
-        <v>-18.07308970099668</v>
+        <v>0.1321839080459771</v>
       </c>
       <c r="H3">
-        <v>-31.72757475083057</v>
+        <v>-0.5804597701149425</v>
       </c>
       <c r="I3">
-        <v>-32.04753325259075</v>
+        <v>-0.5</v>
       </c>
       <c r="J3">
-        <v>-32.04753325259075</v>
+        <v>-0.5</v>
       </c>
       <c r="K3">
-        <v>-11.3</v>
+        <v>-7.49</v>
       </c>
       <c r="L3">
-        <v>-37.54152823920266</v>
+        <v>-0.4304597701149426</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.4</v>
+        <v>6.18</v>
       </c>
       <c r="V3">
-        <v>0.6477272727272727</v>
+        <v>0.06866666666666667</v>
       </c>
       <c r="W3">
-        <v>-4.82905982905983</v>
+        <v>-0.1660753880266075</v>
       </c>
       <c r="X3">
-        <v>0.0563587977563903</v>
+        <v>0.1151094751095153</v>
       </c>
       <c r="Y3">
-        <v>-4.88541862681622</v>
+        <v>-0.2811848631361228</v>
       </c>
       <c r="Z3">
-        <v>-0.3746285818120095</v>
+        <v>0.6954436450839329</v>
       </c>
       <c r="AA3">
-        <v>12.00592193299129</v>
+        <v>-0.3477218225419664</v>
       </c>
       <c r="AB3">
-        <v>0.05632479171699475</v>
+        <v>0.1139203495172394</v>
       </c>
       <c r="AC3">
-        <v>11.94959714127429</v>
+        <v>-0.4616421720592059</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>0.01653754514906939</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.01653754514906939</v>
+        <v>1.44</v>
       </c>
       <c r="AG3">
-        <v>-11.38346245485093</v>
+        <v>-4.74</v>
       </c>
       <c r="AH3">
-        <v>0.0009387511653005391</v>
+        <v>0.01574803149606299</v>
       </c>
       <c r="AI3">
-        <v>0.001572527562239115</v>
+        <v>0.04411764705882353</v>
       </c>
       <c r="AJ3">
-        <v>-1.831157999477338</v>
+        <v>-0.05559465165376495</v>
       </c>
       <c r="AK3">
-        <v>12.88505515129297</v>
+        <v>-0.1791383219954649</v>
       </c>
       <c r="AL3">
-        <v>0.389</v>
+        <v>0.164</v>
       </c>
       <c r="AM3">
-        <v>0.372</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.1815889029003783</v>
       </c>
       <c r="AO3">
-        <v>-24.83290488431876</v>
+        <v>-53.04878048780487</v>
       </c>
       <c r="AP3">
-        <v>1.19411124041235</v>
+        <v>0.5977301387137454</v>
       </c>
       <c r="AQ3">
-        <v>-25.96774193548387</v>
+        <v>-126.0869565217391</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Volpara Health Technologies Limited (ASX:VHT)</t>
+          <t>Adherium Limited (ASX:ADR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +838,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.546</v>
+        <v>-0.258</v>
       </c>
       <c r="G4">
-        <v>-0.05769230769230772</v>
+        <v>-7.582417582417582</v>
       </c>
       <c r="H4">
-        <v>-0.7948717948717949</v>
+        <v>-18.70879120879121</v>
       </c>
       <c r="I4">
-        <v>-0.8461538461538461</v>
+        <v>-18.98355554398209</v>
       </c>
       <c r="J4">
-        <v>-0.8461538461538461</v>
+        <v>-18.98355554398209</v>
       </c>
       <c r="K4">
-        <v>-11.8</v>
+        <v>-6.92</v>
       </c>
       <c r="L4">
-        <v>-0.7564102564102565</v>
+        <v>-19.01098901098901</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +880,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.49</v>
+        <v>3.64</v>
       </c>
       <c r="V4">
-        <v>0.04463722397476341</v>
+        <v>0.2696296296296297</v>
       </c>
       <c r="W4">
-        <v>-0.2185185185185185</v>
+        <v>-0.659047619047619</v>
       </c>
       <c r="X4">
-        <v>0.05662901470710764</v>
+        <v>0.1146188955925291</v>
       </c>
       <c r="Y4">
-        <v>-0.2751475332256262</v>
-      </c>
-      <c r="Z4">
-        <v>0.3363518758085382</v>
-      </c>
-      <c r="AA4">
-        <v>-0.2846054333764554</v>
+        <v>-0.7736665146401481</v>
       </c>
       <c r="AB4">
-        <v>0.05623311733627225</v>
-      </c>
-      <c r="AC4">
-        <v>-0.3408385507127276</v>
+        <v>0.1140997641832703</v>
       </c>
       <c r="AD4">
-        <v>1.91</v>
+        <v>0.059</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.03507109004739337</v>
       </c>
       <c r="AF4">
-        <v>1.91</v>
+        <v>0.09407109004739336</v>
       </c>
       <c r="AG4">
-        <v>-6.58</v>
+        <v>-3.545928909952607</v>
       </c>
       <c r="AH4">
-        <v>0.009942220602779658</v>
+        <v>0.006920008687924657</v>
       </c>
       <c r="AI4">
-        <v>0.04062965326526271</v>
+        <v>0.02409563962275374</v>
       </c>
       <c r="AJ4">
-        <v>-0.03583487637512254</v>
+        <v>-0.3562290120168032</v>
       </c>
       <c r="AK4">
-        <v>-0.1708203530633437</v>
+        <v>-13.42793302105206</v>
       </c>
       <c r="AL4">
-        <v>0.09</v>
+        <v>0.001</v>
       </c>
       <c r="AM4">
-        <v>-0.131</v>
+        <v>-0.016</v>
       </c>
       <c r="AN4">
-        <v>-0.1565573770491803</v>
+        <v>-0.008711058615089326</v>
       </c>
       <c r="AO4">
-        <v>-146.6666666666667</v>
+        <v>-6940</v>
       </c>
       <c r="AP4">
-        <v>0.539344262295082</v>
+        <v>0.5235388911785924</v>
       </c>
       <c r="AQ4">
-        <v>100.7633587786259</v>
+        <v>433.75</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_heathcare_information_and_technology.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2355</v>
+        <v>0.58</v>
       </c>
       <c r="G2">
-        <v>-0.02589506867822557</v>
+        <v>0.256140350877193</v>
       </c>
       <c r="H2">
-        <v>-0.9519252420625985</v>
+        <v>-0.3052631578947368</v>
       </c>
       <c r="I2">
-        <v>-0.8787443266161608</v>
+        <v>-0.2692982456140351</v>
       </c>
       <c r="J2">
-        <v>-0.8787443266161608</v>
+        <v>-0.2692982456140351</v>
       </c>
       <c r="K2">
-        <v>-14.41</v>
+        <v>-5.37</v>
       </c>
       <c r="L2">
-        <v>-0.8111911731591984</v>
+        <v>-0.2355263157894737</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.82</v>
+        <v>5.73</v>
       </c>
       <c r="V2">
-        <v>0.0948792270531401</v>
+        <v>0.02990605427974948</v>
       </c>
       <c r="W2">
-        <v>-0.4125615035371133</v>
+        <v>-0.1721153846153846</v>
       </c>
       <c r="X2">
-        <v>0.1148641853510222</v>
+        <v>0.09296892319132119</v>
       </c>
       <c r="Y2">
-        <v>-0.5274256888881355</v>
+        <v>-0.2650843078067058</v>
       </c>
       <c r="Z2">
-        <v>0.7099920063948841</v>
+        <v>1.745788667687596</v>
+      </c>
+      <c r="AA2">
+        <v>-0.4701378254211332</v>
       </c>
       <c r="AB2">
-        <v>0.1140100568502549</v>
+        <v>0.09273460583917432</v>
+      </c>
+      <c r="AC2">
+        <v>-0.5628724312603075</v>
       </c>
       <c r="AD2">
-        <v>1.499</v>
+        <v>0.8</v>
       </c>
       <c r="AE2">
-        <v>0.03507109004739337</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.534071090047393</v>
+        <v>0.8</v>
       </c>
       <c r="AG2">
-        <v>-8.285928909952608</v>
+        <v>-4.930000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.01460546158143494</v>
+        <v>0.004158004158004158</v>
       </c>
       <c r="AI2">
-        <v>0.04197865876156284</v>
+        <v>0.02702702702702703</v>
       </c>
       <c r="AJ2">
-        <v>-0.08702420571972293</v>
+        <v>-0.02641024267423796</v>
       </c>
       <c r="AK2">
-        <v>-0.3100548895425766</v>
+        <v>-0.2065354000837872</v>
       </c>
       <c r="AL2">
-        <v>0.165</v>
+        <v>0.134</v>
       </c>
       <c r="AM2">
-        <v>0.05300000000000001</v>
+        <v>-0.04699999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.1019519825885874</v>
+        <v>-0.1684210526315789</v>
       </c>
       <c r="AO2">
-        <v>-94.78787878787878</v>
+        <v>-45.82089552238806</v>
       </c>
       <c r="AP2">
-        <v>0.5635536223867651</v>
+        <v>1.037894736842105</v>
       </c>
       <c r="AQ2">
-        <v>-295.0943396226415</v>
+        <v>130.6382978723404</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.7290000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="G3">
-        <v>0.1321839080459771</v>
+        <v>0.256140350877193</v>
       </c>
       <c r="H3">
-        <v>-0.5804597701149425</v>
+        <v>-0.3052631578947368</v>
       </c>
       <c r="I3">
-        <v>-0.5</v>
+        <v>-0.2692982456140351</v>
       </c>
       <c r="J3">
-        <v>-0.5</v>
+        <v>-0.2692982456140351</v>
       </c>
       <c r="K3">
-        <v>-7.49</v>
+        <v>-5.37</v>
       </c>
       <c r="L3">
-        <v>-0.4304597701149426</v>
+        <v>-0.2355263157894737</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,192 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.18</v>
+        <v>5.73</v>
       </c>
       <c r="V3">
-        <v>0.06866666666666667</v>
+        <v>0.02990605427974948</v>
       </c>
       <c r="W3">
-        <v>-0.1660753880266075</v>
+        <v>-0.1721153846153846</v>
       </c>
       <c r="X3">
-        <v>0.1151094751095153</v>
+        <v>0.09296892319132119</v>
       </c>
       <c r="Y3">
-        <v>-0.2811848631361228</v>
+        <v>-0.2650843078067058</v>
       </c>
       <c r="Z3">
-        <v>0.6954436450839329</v>
+        <v>1.745788667687596</v>
       </c>
       <c r="AA3">
-        <v>-0.3477218225419664</v>
+        <v>-0.4701378254211332</v>
       </c>
       <c r="AB3">
-        <v>0.1139203495172394</v>
+        <v>0.09273460583917432</v>
       </c>
       <c r="AC3">
-        <v>-0.4616421720592059</v>
+        <v>-0.5628724312603075</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="AG3">
-        <v>-4.74</v>
+        <v>-4.930000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.01574803149606299</v>
+        <v>0.004158004158004158</v>
       </c>
       <c r="AI3">
-        <v>0.04411764705882353</v>
+        <v>0.02702702702702703</v>
       </c>
       <c r="AJ3">
-        <v>-0.05559465165376495</v>
+        <v>-0.02641024267423796</v>
       </c>
       <c r="AK3">
-        <v>-0.1791383219954649</v>
+        <v>-0.2065354000837872</v>
       </c>
       <c r="AL3">
-        <v>0.164</v>
+        <v>0.134</v>
       </c>
       <c r="AM3">
-        <v>0.06900000000000001</v>
+        <v>-0.04699999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.1815889029003783</v>
+        <v>-0.1684210526315789</v>
       </c>
       <c r="AO3">
-        <v>-53.04878048780487</v>
+        <v>-45.82089552238806</v>
       </c>
       <c r="AP3">
-        <v>0.5977301387137454</v>
+        <v>1.037894736842105</v>
       </c>
       <c r="AQ3">
-        <v>-126.0869565217391</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Adherium Limited (ASX:ADR)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Heathcare Information and Technology</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.258</v>
-      </c>
-      <c r="G4">
-        <v>-7.582417582417582</v>
-      </c>
-      <c r="H4">
-        <v>-18.70879120879121</v>
-      </c>
-      <c r="I4">
-        <v>-18.98355554398209</v>
-      </c>
-      <c r="J4">
-        <v>-18.98355554398209</v>
-      </c>
-      <c r="K4">
-        <v>-6.92</v>
-      </c>
-      <c r="L4">
-        <v>-19.01098901098901</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>3.64</v>
-      </c>
-      <c r="V4">
-        <v>0.2696296296296297</v>
-      </c>
-      <c r="W4">
-        <v>-0.659047619047619</v>
-      </c>
-      <c r="X4">
-        <v>0.1146188955925291</v>
-      </c>
-      <c r="Y4">
-        <v>-0.7736665146401481</v>
-      </c>
-      <c r="AB4">
-        <v>0.1140997641832703</v>
-      </c>
-      <c r="AD4">
-        <v>0.059</v>
-      </c>
-      <c r="AE4">
-        <v>0.03507109004739337</v>
-      </c>
-      <c r="AF4">
-        <v>0.09407109004739336</v>
-      </c>
-      <c r="AG4">
-        <v>-3.545928909952607</v>
-      </c>
-      <c r="AH4">
-        <v>0.006920008687924657</v>
-      </c>
-      <c r="AI4">
-        <v>0.02409563962275374</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.3562290120168032</v>
-      </c>
-      <c r="AK4">
-        <v>-13.42793302105206</v>
-      </c>
-      <c r="AL4">
-        <v>0.001</v>
-      </c>
-      <c r="AM4">
-        <v>-0.016</v>
-      </c>
-      <c r="AN4">
-        <v>-0.008711058615089326</v>
-      </c>
-      <c r="AO4">
-        <v>-6940</v>
-      </c>
-      <c r="AP4">
-        <v>0.5235388911785924</v>
-      </c>
-      <c r="AQ4">
-        <v>433.75</v>
+        <v>130.6382978723404</v>
       </c>
     </row>
   </sheetData>
